--- a/data_segmento.xlsx
+++ b/data_segmento.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R05ce96332a41442e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="1" r:id="R8894de1d8c8f48dd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -161,37 +161,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>25273.27010251398</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.00472512121583879</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0163964230126743</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.017130611505184357</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.042261937087471946</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0606883340650437</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.26426922480865866</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.58578592776253746</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.45019380547686993</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.025293426589552061</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>2.8589227830931283</x:v>
+        <x:v>24349.265450489238</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.004769218879139725</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0030500922485803272</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0058916859090631934</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.022250800611468335</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.033132576964548077</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.27274983488305216</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.596423244443919</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.48462308906049678</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.023767735006290914</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>3.2685000477166408</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -216,37 +216,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>28842.889300474159</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0060424724023304677</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.020927807976825585</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.019025728930949226</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.055276264592406088</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.091332401114809558</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.29526736332018322</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.69737542251998219</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.66111880377639465</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.033487333385546665</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>5.00035910173043</x:v>
+        <x:v>29526.487103155723</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0064258385315032474</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0017184311145650444</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0017963042681916619</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.024821703109968229</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.03946832135392242</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.30095984705692391</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.70483510402007865</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.65968793429647166</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.027967164991656891</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>5.1663997689793133</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -272,34 +272,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0043450841037073751</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.014133131321101278</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.021890613378383383</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.046158888462919156</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.079870392484268748</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.19849024697942474</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.27882741851900028</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.33239396536779631</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.013739143696137868</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>23.246878760872743</x:v>
+        <x:v>0.0047038600067303982</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00067062926107697152</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.020715831524342088</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.040724545396686018</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.064593520460520137</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.23076797880996569</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.31326879055063084</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.33700269440561859</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.011596658221643893</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>23.469265435837279</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -324,37 +324,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>2473852.8314484376</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0046258280666153784</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.014383114701666422</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.015277029185924551</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.035938481757619378</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.053763414609943494</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.24154407908661857</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.59296786874992224</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.57201380266292</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.018753996891208952</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>4.6803758559828541</x:v>
+        <x:v>2471416.4899103693</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0065969519314772462</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0019035838987737641</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.010630055278168182</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.02716028814117899</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.038537914664947381</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.25847477085121451</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.61469085743072061</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.58551468232695858</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.025309550303194789</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>5.1216064865518875</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -379,37 +379,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>1049709.9135593264</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0050076185314633648</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.015537331367201812</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.016106772330861663</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.038066581751595052</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.056471692036288657</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.24227856315756036</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.62187220651140906</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.56624230921807794</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.01948825468846509</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>4.1786738407440982</x:v>
+        <x:v>1059621.8993789593</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0063842940426543926</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0018575809471468308</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0088885945161807367</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.026977918446102978</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.038889992041677646</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.25756008461913238</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.64182318664322024</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.58033689934758814</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.026393766409895637</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>4.5537372352763335</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -435,34 +435,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0069407227889750622</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.018255013809918008</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.021267356006547056</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.04311748399112858</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.061269960196655759</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.25198976830889142</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.62107213595826516</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.62194696832059471</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0211220236752517</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>5.6521717957487567</x:v>
+        <x:v>0.0044063015234836467</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0010018864026144492</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0091085199053977384</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.030349640113196186</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.04293661194735976</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.26876598304485277</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.64279392230485266</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.61754613828484972</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.026811517327869898</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>6.1153195067866717</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -488,34 +488,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0031784198038586897</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.005248831683210442</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.016937848936322331</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.053851540711285617</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.075884222343660213</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.10215592826054531</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.17968603015039109</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.24308190323291634</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.028020494600227631</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>3.0433223561832765</x:v>
+        <x:v>0.0027482794300881519</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0014157610869933723</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.018524739774594012</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.028719656511078551</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.064485989019078538</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.13008614312341593</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.20958096919484026</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.21941866561256629</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.018798550216078184</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>2.9536039364481588</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -541,34 +541,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.00445394018923273</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.013025424992256562</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.017157714988578654</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.034446734025922021</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.052891713526802331</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.14801971097042133</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.25679312429429979</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.35622596523135064</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.01886778418275481</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>8.5761174269895957</x:v>
+        <x:v>0.0041407408759772668</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00061651119789041253</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.016836964095454876</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.036191835248085</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.053273856196140335</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.17537399667026676</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.28673919391229208</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.33179449475128164</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.01891316099752733</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>8.2579175225391666</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -594,34 +594,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0043109817874777967</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.010382266770294413</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.019704065933717319</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.053883561319990392</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.078592153750949967</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.1792962618527989</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.33606047560411723</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.42246607200190445</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0428227836526228</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>4.7813101567966108</x:v>
+        <x:v>-3.1269497376973376E-06</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.0057438257858062336</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.019413880413149176</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.020303376997077738</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.051641280156484504</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.19390010548925884</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.35260561265383727</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.39412882367759927</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.051168934670336327</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>4.4822443136458352</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -647,34 +647,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0014155341753137041</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.025629235959100383</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.034976517771855953</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.063282736521132144</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.080455811439303471</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.11322669545322528</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.18555519488311045</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.25386211081837184</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.044678870734266109</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>4.6559820712865649</x:v>
+        <x:v>0.0025771006024453147</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0013128633258969735</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.017033024118738416</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.046223348780123352</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.071994970548858284</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.13774792856445672</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.21166962011087098</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.22772399884870054</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.015425146737386951</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>4.5503988597939573</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -699,37 +699,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>16360.334473348848</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0049803247513084958</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.016636448208203536</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.018314015897799241</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.044575004209565394</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.059142997740314396</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.19358042663695985</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.45882140442972408</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.44749909670182064</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0265427413516129</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>3.9916389166730228</x:v>
+        <x:v>16587.162276425111</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0050952853768266859</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0021932066902741187</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.018720013287936377</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.028109154590276075</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.047661724674616046</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.2099835027096888</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.47886962065325012</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.45667909974528476</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.031533390422859769</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>4.3331935156383725</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -754,37 +754,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>1.9139224212575499</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.010778511072088715</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.02953903273077485</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.051881130197685033</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.10855775078588903</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.14811387934817488</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.25913650848191183</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.30134889538812504</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.35252167560645964</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.037448562863974182</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>-6.8609605859381224</x:v>
+        <x:v>1.77281606963751</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.011863593555868968</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.0030603964783877391</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.057389437231452067</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.098022178888582889</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.15337359153803798</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.313757606586773</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.35285783186963482</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.3635201731612443</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.03364855340117303</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>-7.1753998042182783</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -866,37 +866,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>9585.3019349463211</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0012809496306109835</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.010422291542546924</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.022164021771445386</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.049273473109605392</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.062249908195908032</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.21757635238980422</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.46369950372519408</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.37187020214156252</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.027671351656669046</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>3.344631345541802</x:v>
+        <x:v>9209.7679384539642</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0044937884601354838</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0033133009800192514</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0042023838451132889</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.00819997824585239</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.036208487973983683</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.21977968553343485</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.46634822273369303</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.3808309837367525</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.029839033747237034</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>3.6149951497163073</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -921,37 +921,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>24002.216071613449</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.00097298187024930094</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0089057672814643052</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.023525287418245666</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.063056716865162121</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.10531934094314011</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.28969394618813604</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.56413047414563589</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.61459826662260619</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.032198784886662835</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>9.3098069542586774</x:v>
+        <x:v>20316.017722616387</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00696527514438583</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0019468652742276049</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0088374127772712363</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.016110676402514068</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.052386832348226164</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.30083272364652869</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.57763949411032822</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.56834298813910711</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.030881618927329813</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>8.7741167835792186</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -976,37 +976,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>6944036.90893544</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0033330634960246908</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0085581733857520437</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.013454355496612003</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.031674594816883062</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.044362192072842754</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.12038660031989057</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.23849135543471722</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.293021587114231</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.010481805368369328</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>11.075636286540234</x:v>
+        <x:v>6812678.5520226862</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0036890862586331785</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00097650848715447047</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.012380150013697078</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.023471528921983564</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.038220621735599369</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.13819957030452423</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.25892133098664782</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.28233584454739091</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0099343867426224548</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>12.164349602611157</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1031,37 +1031,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>237151.14343557297</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0021432852324585472</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0042606371994393655</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0089442415977643019</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.026062750320789752</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.039095487268983709</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.091983728330733872</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.15767240896174584</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.1984508731571617</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.010286397332388085</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>7.3031525091581644</x:v>
+        <x:v>260493.82383737192</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0033855524558492611</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00074953186018578144</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.012643636933967528</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.021071676756074131</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.037419989963470179</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.11049261886278128</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.17729470857439655</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.19703207700945269</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0099234717428298355</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>7.9301884783187333</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1086,37 +1086,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>1002707.2686512601</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0015791943174838785</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0086567306110389985</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.016663485037277992</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.047526380032583582</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.063154047623577236</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.17299602846142847</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.35798003931389277</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.41487981329425794</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.018322934543516686</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>6.4922487349187614</x:v>
+        <x:v>1017337.6623877621</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.006457913505863333</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0025572961402655636</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.010332736738135617</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.019806768032340605</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.045154428775331823</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.18772628846018691</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.37503329317567724</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.39186999766402786</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.022422381032943205</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>6.6217607693581568</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1142,34 +1142,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>-9.0879849362623943E-05</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.008810532745506805</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.018217007350553205</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0493151886621761</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.059670032685273267</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.16880764916704694</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.36800921754098259</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.47764426363839108</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.026441889628303933</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>5.3516775869998146</x:v>
+        <x:v>0.0036314602284606146</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00067300798044356291</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0071255676854504735</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.017426289468376766</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.041395165161838055</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.18063799092655208</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.38185582145839936</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.40265247039665852</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.027461810543588195</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>4.9745995333032251</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1195,34 +1195,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0041219889831560774</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.012124243860475836</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.018506366851140488</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.035394879199644125</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.053623306170571094</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.14993697053265476</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.25568627163143942</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.37305340911510121</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.010399497849738272</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>23.50644647682229</x:v>
+        <x:v>0.0044657148308944183</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00063013698630132176</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.020146072063675247</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.038122026484179505</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.055785775031883977</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.18015124198672017</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.28867907631937118</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.33826436973163765</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.010533657528573414</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>23.25555482805715</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1247,37 +1247,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>31154.409655478808</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0050046203676126222</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.011850469246062145</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.018557709913590292</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.034912404579892531</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.051196387779767649</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.17772571401764425</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.30170547443793194</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.40351070806436939</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.014802057772634587</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>13.8732075536794</x:v>
+        <x:v>31587.842087782657</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0076389857581840026</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00048718350033105651</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.022483839661620708</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.038185147095700422</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.055001129592548992</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.20987543975702905</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.33723961748883924</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.39056463828054122</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.01874183628608083</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>14.347389378307271</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1302,37 +1302,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>701025.66439275409</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0048427405216306951</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.012064677691093983</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.018207465078919904</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.035594762386484513</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.053046798767162784</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.16648600814949677</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.26302741486255465</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.37256828665892749</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.010342615911878326</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>15.693294836133973</x:v>
+        <x:v>642883.24169790291</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0059148728084168489</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0011034962955640548</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.020253098182622109</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.035752453800642181</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.053031926681845087</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.19474977902522017</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.29363036870343562</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.34450500508608317</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0106119310542901</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>15.270169800841831</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1357,37 +1357,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>641543.45734247169</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.00488153792518764</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.012060933111785133</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.018843193881433073</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.036131882000364213</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.054471841635172158</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.17026828847052777</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.26510397971392474</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.37764960433153005</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.010561384105569473</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>15.864586701909504</x:v>
+        <x:v>576466.93992365012</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0057055110761461414</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00087306209531257117</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.020136631036534069</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.035868248907349631</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.053544376182119935</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.1986045061055961</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.29573649539715863</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.3485484968364696</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.01041613305682557</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>15.39846153045962</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1413,34 +1413,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0045069686456233882</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.01328884946115938</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.020292733811163588</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.038859366897977088</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.058886935171735821</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.162790202090203</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.27606220146465721</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.40076583928568144</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.011404799746914142</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>23.942505981631907</x:v>
+        <x:v>0.0048508074454316485</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00068493150684956206</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.021935224899058747</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.041652563049019209</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.061118228308582934</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.19608989834123447</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.31260575302693594</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.36527656827240929</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.011498986026844234</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>23.683524985545226</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1466,34 +1466,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.005699320259239915</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.014283305874029928</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.019011268112962165</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.036358159132937384</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.055871913331675405</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.18782096631611789</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.33300990860523605</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.39796843656247027</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.016631893949214577</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>5.3747725175917278</x:v>
+        <x:v>0.00661224098899571</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0013523881540198346</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.015885505700874658</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.030164539191438022</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.046714239248403677</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.20760779698056719</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.35521530999447637</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.40192631676321988</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.020673456589576752</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>6.15914647081899</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1519,34 +1519,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0047541870076044379</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0139209738604269</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.01578278024910329</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.02902800165717867</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.050373942574667652</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.18670672534954691</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.30266226637206195</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.40911334581271941</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.015618062163166207</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>12.072095539524593</x:v>
+        <x:v>0.0048704720450942762</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0014267600539970005</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.021215114759040254</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.039178221028836946</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.051043976750543063</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.21898769634541537</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.33809747706051785</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.37406013795942994</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.018145539898946378</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>11.152835725066025</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1571,37 +1571,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>53010.471912334855</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0038561276480495454</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0086859973053232675</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.01197151470342761</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.031687372039813422</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.048848609033824264</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.19190972061406253</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.40213706265735749</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.35938403579947331</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.014280651538332035</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>4.3244677380930083</x:v>
+        <x:v>55117.7852160119</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.007601795289714719</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0020506549981789135</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.018933824895190021</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.030916910179825452</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.045231848342695</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.21866928950229858</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.43361644626335605</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.39136517668060722</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.019087931832935411</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>4.9544350851413919</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1626,37 +1626,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>34939.221097467271</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0058686178268370082</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.012916491851508338</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.019653039166581232</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.039824830509563647</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.059887490969164237</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.21722645118996931</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.35648747385468904</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.473246406976342</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.01642331173397002</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>12.11918687496579</x:v>
+        <x:v>37798.337431638749</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.009333969930682251</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0015528554536359263</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.021025360872602317</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.037117637290479566</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.058223978372297092</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.24808038922305276</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.3908713639024699</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.43710654956892503</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.017382593194836538</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>11.4622408418511</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1681,37 +1681,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>30583.683134820512</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0053502673111325283</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.016512566069615486</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.025958540490828019</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.05184808379384509</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0880342982007043</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.23710209658779924</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.39235119649840056</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.53410424799431011</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.026409129444015297</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>13.887752104606676</x:v>
+        <x:v>25375.083559443861</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.010461622221965339</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0025916235703271617</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.016171759432423993</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.031393368123885379</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0518067817169392</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.25634504836839289</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.41400902652695781</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.47516356141064997</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.022864938886491607</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>12.45329089415991</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1736,37 +1736,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>5732064.285705246</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0043998989347098227</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.011567102707399135</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.016809952100431014</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.034021942893239343</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.051168740508610755</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.17040747630806274</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.29154602602844903</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.37424179966413251</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.01124229442659196</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>12.801697198164092</x:v>
+        <x:v>5738824.2166226553</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.006012012690298274</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0010001727808237604</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.016749347864805086</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.03167848600087253</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.047303170081169688</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.19329963256460703</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.31745217549242621</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.35553455334406503</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.012714469537841054</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>12.594879589410057</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1791,37 +1791,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>3535602.8113623783</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.00487819020545599</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.012746173034421604</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.018380010748614284</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.036806754873241365</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.055682481251975835</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.19762181542866131</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.37275739583439127</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.44412393141876372</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.012995734214750887</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>9.2647212069455129</x:v>
+        <x:v>3373689.0427758433</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0061358964565989549</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0010130339726417414</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.017395660178902039</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.033593169758783237</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.05041391212362889</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.22115324182479612</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.40274799331853228</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.428020203798098</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.015162874380047448</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>9.2106445669872787</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1847,34 +1847,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0055013091657676316</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.013061692392314583</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.020485664229936251</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.03667262281372019</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.052595141985068539</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.19122015713073193</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.3142436952721106</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.42825853494256494</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.01343299320511066</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>14.098709990769</x:v>
+        <x:v>0.0059655410402603692</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0012704875195421739</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.02046106029740824</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.035118983643577018</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.051728966448122859</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.21830045267579279</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.34412071462336691</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.39721734301340605</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.014041963553054766</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>13.615677453966208</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1900,34 +1900,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0056566988678641295</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0150145570471234</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.02008772213333776</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.034774247114074841</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.051609642788700061</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.23074168726835587</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.457020359137982</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.49370328344948566</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.015227888289480337</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>7.5439530436099176</x:v>
+        <x:v>0.0051601930682898534</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0007460445296878504</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.015409682707308248</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.033448758160504966</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.04613548676576551</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.25471293564366304</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.4853988542178842</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.47985904168718863</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.017866035150818992</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>7.6381967536377067</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -1953,34 +1953,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0037091358424337084</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.010905548557436306</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0166409028070873</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.031800655403553479</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.04813547001039753</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.13398830466106526</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.22743004113589138</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.33022365276076648</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0093588080465900562</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>23.122462876689291</x:v>
+        <x:v>0.004018375540586927</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00056712328767116738</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.018113905099377714</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.034246375448841126</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.050071456743032927</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.16076995094114643</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.256418521052421</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.29984848148919174</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0094795477177366926</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>22.907533763564107</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2005,37 +2005,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>300642.50542605075</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0042688454067418835</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.011705280593550471</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.018657724113864127</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.036080071324951168</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.054274213443427088</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.15504829694720867</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.29503555123989722</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.38278499112207331</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.011219813029479837</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>20.646797216611287</x:v>
+        <x:v>312121.5375105117</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0049233798891383795</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0006493609870747985</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.018236014034027415</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.03496445786078306</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.053644006422721935</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.18282113845664805</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.3261743505513508</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.37211865986132042</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.010692986787772195</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>20.390897780583224</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2060,37 +2060,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>4056050.8853577957</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0045986193232365746</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.011688608411052126</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.017427846865125218</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.035273526838368596</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.053515999679022208</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.16052843500588376</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.26903111897310095</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.37397852930519782</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.00914803860849631</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>22.512601549408693</x:v>
+        <x:v>4019104.0908920895</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.005161049140581353</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00067317932140786851</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.01871067880770183</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.035859002812543839</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.053044618118351705</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.18949423001504195</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.30031623906269056</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.34965102320942409</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0091919516993476443</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>22.045654317560423</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2115,37 +2115,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>252655.89546886008</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0050087753952072767</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.01166268890453992</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.020501513718145015</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.039092153736798307</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.058173813086887849</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.1673675002869206</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.29838173629347775</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.41572800578048286</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.013465367556940805</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>18.236758650554467</x:v>
+        <x:v>215152.54676218575</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0062016895770034</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00081863823731942453</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.01948661242152383</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.037839985304344959</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.058616049900732659</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.20018760690120363</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.33646196127159977</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.40593663964084925</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.010644204231899766</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>19.785386981665919</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2171,34 +2171,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>-0.0028497234031317209</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.000427300533463848</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.016663897131679484</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.064588034568380248</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0697954291204872</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.04684651989507671</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.20356007970291046</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.25079226334774241</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.046015237748488313</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>2.7091544670972842</x:v>
+        <x:v>0.00021382746147868836</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0017140833635267416</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.0043462562928947568</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.0049417789776221577</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.041234128293069938</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.044778436563702284</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.2011824030408238</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.20985080101159093</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.042703984758651926</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>2.4163566340483937</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2223,37 +2223,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>5896.5824504658276</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.0099458266693543962</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.00044526061143146389</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.019342769171834862</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.078253073958524544</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.09055458572426911</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.044094661557378956</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.070576320686696281</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.15424203373191903</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.063436222778910922</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>1.0850224068343033</x:v>
+        <x:v>5833.7022326668193</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0077734142645717874</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0051438136140682378</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.014800348064257784</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.016122934430616187</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.079736208024607569</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.071299912204295879</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.098471585563821851</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.15347608889880449</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0411572240386667</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>1.1703139663523228</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2278,37 +2278,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>9682.5900588373115</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.011972125423143187</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.00897234290887583</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.00857821216166088</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.056306910742589089</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.06969131301046394</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.010075295873730017</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.034595300903391024</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0038614666948937337</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.054190582315834138</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>0.029487549127173725</x:v>
+        <x:v>8543.459665995566</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00074498054161242777</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.00083430388784222487</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0060583884626859152</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.0071332495588789513</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.033223657721799027</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.014950201647209171</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0395885470764159</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.009187874380466754</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.036902833395651778</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>-0.073076725763644934</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2333,37 +2333,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>2031.8218908100898</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.002486851195884543</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.00857719807410473</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0018776683394363669</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.038753630416114682</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.051406997718997705</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.016971467162301135</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.037270952365172638</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.10467998385553523</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0428335385809787</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>0.86934569871992828</x:v>
+        <x:v>440.663543599846</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.001599721611954541</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.0011548722140501955</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.011191162044863034</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.00802529787322559</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.043421749564590328</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.034181256613873057</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0548242616475334</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.077606946339155991</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.033165742211098824</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>0.69176115223202339</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2389,34 +2389,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0020089679700918683</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.0035871402391260965</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.011950147159752733</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.061436081284583555</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.071533508970947679</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.012527813338027327</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.081309862340626315</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.14906687402799323</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.051045533820759714</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>0.93813096715424038</x:v>
+        <x:v>0.00079244073200901433</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0021608929129097731</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.016310423217231085</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.016777739017279414</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.06420352154449871</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.036530827693008527</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.10694342598800843</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.10324324533260509</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.034413570669760189</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>0.69849230178345079</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2441,37 +2441,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>1120.34704732413</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.0055301579594470018</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.015109718299536778</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.007477255192070098</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.050543739073707572</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.059461567757757017</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.020774664322320557</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.12150026202540243</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.18102810433824579</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.053577196532802109</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>1.3851517052948785</x:v>
+        <x:v>1056.6829583922026</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.0094932523582346162</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.008215318830273155</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.003650457913304872</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.008612814396096069</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.033797298790962493</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.023163899487301354</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.12412525650970929</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.11440746727391571</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.063810115826970618</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>0.91618587857430889</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2496,37 +2496,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>23848.338884126228</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.0045049902845426537</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.0017849587532829947</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.024087305290222849</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0795530788934764</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.097040092053369165</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.074310474809331062</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.16497960531269396</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.26469374259217671</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.056197785426192651</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>2.0633681055839346</x:v>
+        <x:v>23007.318822118919</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00083418449832350916</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.0018597929086272558</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.01477128556661067</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.019228113542047565</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.090859559915214438</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.096925405202089587</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.18950317955021223</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.22138924966911588</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.052993720186200306</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>1.8077799631840761</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2551,37 +2551,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>1418307.1169978858</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.0027959780173504312</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.0024602063520826611</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.010584734114140293</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.048245919945580029</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.058948561510638431</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.069981605574176431</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.13632394057905972</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.22667349199112241</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.030318475391831894</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>3.0603358279158837</x:v>
+        <x:v>1397757.852499967</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0027395772741281021</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00082284898264295414</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.011133291158970549</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.013654461703851428</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.05073344081953346</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.088647628976275872</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.15590121765188525</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.19950673609492631</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.020064693932358532</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>2.9093678330006689</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2606,37 +2606,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>302797.14687791112</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.0047732641834870027</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.0061019684944173536</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.010789920600720704</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.059130699823309207</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.07031182093467514</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.035137470420432582</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.11929471049626672</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.21752471022633446</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.042697638591297493</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>1.9642311533033456</x:v>
+        <x:v>325145.01182728063</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.002999455335408463</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0011525621557368915</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0077589270647984154</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0051904114588541272</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.048853081082357752</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.047920002209005164</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.13311646908055264</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.16333304142540195</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.031545184378626169</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>1.5932700370001318</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2662,34 +2662,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.007323720388831001</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.013306228498670469</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.015219473010910534</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.078898417268898235</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.08672431447323925</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.086600399392280369</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.29608528328916539</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.35326159282930991</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0677370631401262</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>3.7368460668477423</x:v>
+        <x:v>0.0039211878789056076</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0012221231553430911</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.00710913921626688</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.013650829920623053</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.035282759799265984</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.085561654020554379</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.2948473654463204</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.31308289320776339</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.052188147368039707</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>3.484396745453048</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2715,34 +2715,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0047666003004209756</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.009046475700666079</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.016151097607778775</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.031926557450214554</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.045427499372016955</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.14543058865622127</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.22388700243069759</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.33179099999999995</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.017131212177314351</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>10.536975140392995</x:v>
+        <x:v>0.0035774995851693969</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.00037536627594780825</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.016190939883985678</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0325950207531851</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.045753934374200389</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.17040265795360621</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.25056953678899796</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.29562373551043719</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.017795452601231838</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>10.663716781074202</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2768,25 +2768,78 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0049390218472773473</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.012744413014746714</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.018955603127678078</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0364347592995542</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.056411276148842227</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.15002671789229471</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.262020642622264</x:v>
+        <x:v>0.0045496671391236365</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00077796479781588879</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.019985999042039682</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.038244504701148152</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.056556937831182541</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.17965417587446764</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.29453333383212832</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.32639934991509789</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.010115372432246942</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>2.7750186863709478</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="6" t="inlineStr">
+        <x:is>
+          <x:t>ARS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="6" t="inlineStr">
+        <x:is>
+          <x:t>Renta Mixta</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="6" t="inlineStr">
+        <x:is>
+          <x:t>Discrecional</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="4" t="inlineStr">
+        <x:is>
+          <x:t>Compass Renta Mixta V</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8"/>
+      <x:c s="9">
+        <x:v>0.0028270316451561861</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00077896179971315149</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.017673208387740891</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.026451342371246467</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.075207854021351439</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.069155954196625125</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-1</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -2794,7 +2847,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>0.009957808333661694</x:v>
+        <x:v>0.093489868136444</x:v>
       </x:c>
       <x:c s="11" t="inlineStr">
         <x:is>
@@ -2820,27 +2873,27 @@
       </x:c>
       <x:c s="4" t="inlineStr">
         <x:is>
-          <x:t>Compass Renta Mixta V</x:t>
+          <x:t>Compass Renta Mixta VI</x:t>
         </x:is>
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>-0.0040356870315980675</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>-0.0048867398256702277</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.012102221499622923</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.061545950437480457</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.075460674486711232</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.03608044641344077</x:v>
+        <x:v>-0.0038072906056885181</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.0014587410779171028</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0027902070537795254</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.01632466369178065</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.065701911904510357</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.13057423223696163</x:v>
       </x:c>
       <x:c s="10">
         <x:v>-1</x:v>
@@ -2851,7 +2904,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>0.056228632350665247</x:v>
+        <x:v>0.072863598791316</x:v>
       </x:c>
       <x:c s="11" t="inlineStr">
         <x:is>
@@ -2877,27 +2930,31 @@
       </x:c>
       <x:c s="4" t="inlineStr">
         <x:is>
-          <x:t>Compass Renta Mixta VI</x:t>
+          <x:t>Compass Renta Mixta VII</x:t>
         </x:is>
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.00082119918492384869</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.012134876889188018</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.032253420929943211</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.078845758125196452</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.086489397890917363</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.12209804752963027</x:v>
+        <x:v>0.0075725700619189151</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0011393956324123877</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.016164725417178394</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.025134597148969817</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Infinity</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Infinity</x:t>
+        </x:is>
       </x:c>
       <x:c s="10">
         <x:v>-1</x:v>
@@ -2908,7 +2965,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>0.052288914156233456</x:v>
+        <x:v>0.023259953416080139</x:v>
       </x:c>
       <x:c s="11" t="inlineStr">
         <x:is>
@@ -2938,37 +2995,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>5030.2027383212717</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0015679925465492683</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.015416553921497655</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0178608025806255</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.060265602055454837</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.072640500429665744</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.19127725451024036</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.55392906823252264</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.41110856315319055</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.053842303745045755</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>2.7728777216631104</x:v>
+        <x:v>4924.0893740172714</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0079275549102300058</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00387349662736991</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.0043505281611274649</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0080081915889362865</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.020243101340545078</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.18435831329310104</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.54490384439147377</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.42973518481121453</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.041403187909195012</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>3.0044692826264932</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -2993,37 +3050,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>9999.9443337066114</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0024274447460825854</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.013854553516891688</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.018035845543880935</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.064340381256275059</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.073876238160360153</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.18705625118535707</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.52489966099170138</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.38857737201514375</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.051774664670355429</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>2.7855416801116997</x:v>
+        <x:v>9725.17770926586</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0077448957078900538</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0032963941970496347</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.0055369409138263936</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0022573158187642051</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.021519434441295227</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.17527536004507271</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.50976585676965169</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.40102665251443281</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.040667791158172248</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>2.9837643842731834</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3105,37 +3162,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>3950291.8724870859</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0037187903238680153</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.007839693431525685</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.011660483656549259</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.029174367997495176</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.035410431950175347</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.089542608068664542</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.21627761137460433</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.25021417322964812</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.011947321846899601</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>7.7860866808683742</x:v>
+        <x:v>3986569.5280804029</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0033714199861514249</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00088947663351146566</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0099918234869389444</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.020808320811130043</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.032293418322774325</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.10487299115046711</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.23332468865426192</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.2456007496166599</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.010303856537401818</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>8.5226780601967054</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3160,37 +3217,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>1033966.2848156836</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0040278593853204647</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.011820963076525359</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.015678632971197981</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.054315100467508426</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.065919122990982792</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.12418318821111596</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.32682495814420576</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.35412041131568617</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.032585885955480565</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>5.6036464244773789</x:v>
+        <x:v>989097.45439351315</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0054562530373394313</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.001538319915418862</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0024825826805869866</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.018002981520035988</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.036583634346031069</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.13076418005001056</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.33459221913223347</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.32722902135543852</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.026566037816740173</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>5.5814295813117241</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3216,34 +3273,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.006266138248016917</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.015411094037332873</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.022217801513754853</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.058009682612111479</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.07055815667092924</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.14235310478230012</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.31601958855960732</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.35290617014037706</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.023636588691292957</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>4.9099175133878488</x:v>
+        <x:v>0.0064665073293312947</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0015862068938161666</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.010910110644296811</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.029227845878053049</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.05273026038287032</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.15879657584174489</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.33496288194897184</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.34016288361455116</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0225699877970121</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>4.9691898489321051</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3269,34 +3326,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.00406708305253356</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.010196226019118182</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.016149469879848333</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.032199283486687769</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.048988946513699005</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.22103463982979799</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.44537582810377407</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.47875414567214336</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.015045771141700397</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>6.892374387427072</x:v>
+        <x:v>0.0053283531903263182</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.001080356600895449</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.016802933092554984</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.030574285167155324</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.042689020274059741</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.24703326294427885</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.47615118875929885</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.46856769030582779</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.017467765299970402</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>7.5721685295977723</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3322,34 +3379,95 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.0096313431998831245</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.020167048258719289</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.025173352566901341</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.057012327075455893</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.069230828730281191</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.10601121307652517</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.31766439152961734</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.421398931885967</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.030710042794862568</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>5.4698987925571085</x:v>
+        <x:v>0.0029890631340236951</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0011209396693736551</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0075433988185122924</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0321574583700448</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.046926755540322329</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.12006939452288812</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.33441283393465193</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.3645466179991137</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.029645150910579177</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>5.1957150026753833</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="6" t="inlineStr">
+        <x:is>
+          <x:t>ARS</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="6" t="inlineStr">
+        <x:is>
+          <x:t>Renta Mixta</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="6" t="inlineStr">
+        <x:is>
+          <x:t>Discrecional</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="4" t="inlineStr">
+        <x:is>
+          <x:t>Toronto Trust Dinamico</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="8"/>
+      <x:c s="9">
+        <x:v>0.014917953715461341</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0026168031631130795</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.026416886259854389</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.031075932277968343</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Infinity</x:t>
+        </x:is>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Infinity</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c t="inlineStr">
+        <x:is>
+          <x:t>Infinity</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.058780834344229427</x:v>
+      </x:c>
+      <x:c s="11" t="inlineStr">
+        <x:is>
+          <x:t>nd</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row>
@@ -3370,26 +3488,26 @@
       </x:c>
       <x:c s="4" t="inlineStr">
         <x:is>
-          <x:t>Delta Gestion XIII</x:t>
+          <x:t>Delta Ahorro Dólares</x:t>
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>2.3700687403223997</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0014578193427690067</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0025428470216521948</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0035013625189266318</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0059664429663104368</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0110719467559377</x:v>
+        <x:v>3.6761190772627694</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0027070536903901488</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>1.3739350776420522E-05</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0035583017849616372</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0054734478083513505</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.007821362764655948</x:v>
       </x:c>
       <x:c t="inlineStr">
         <x:is>
@@ -3405,7 +3523,7 @@
         </x:is>
       </x:c>
       <x:c s="10">
-        <x:v>0.003392879238616905</x:v>
+        <x:v>0.0048639969243783887</x:v>
       </x:c>
       <x:c s="11" t="inlineStr">
         <x:is>
@@ -3436,34 +3554,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.00082401503249851515</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0016320191757435154</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0021910566715410695</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0043597167198468068</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0065465529426571578</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0152808918540972</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.023340508819745809</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.028766051092369738</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0013282443809860196</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>19.9768865809907</x:v>
+        <x:v>0.00032255091696620219</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>4.9904988579374532E-05</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0016119497671467364</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0038370057675505276</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0057855020761785614</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.017585525339249841</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.025663437205635242</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.027674361495545696</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0012733998140055452</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>19.515582819500679</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3489,34 +3607,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.00089469291370636306</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.00046699495360580379</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>6.00032544137985E-05</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.0014632709843822589</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.0027291258886645853</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.0092302267002518645</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.012692021928151109</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.015656970109511614</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.01069567914857685</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>-3.4436585397874424</x:v>
+        <x:v>0.0034663208482721419</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.0017080335252173118</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0055906749376719578</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0038185647568755865</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0021768721303481176</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.005961712846347611</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.0094349284122171584</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.010686494725442253</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.40710415460499988</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>-0.064733852056193711</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3542,34 +3660,34 @@
       </x:c>
       <x:c s="8"/>
       <x:c s="9">
-        <x:v>0.010806300807075786</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.029458222502395826</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0062691182054912531</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.0055164150728541639</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.026973400570645234</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>-0.0041980728921886534</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.027119899039277584</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0043239999999999945</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0924295502810726</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>0.022781705505402358</x:v>
+        <x:v>-0.0063948618536951995</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.0050315704429811925</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.0014927727830077453</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.026135756115530873</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.013303666574574824</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>-0.0084883566438420655</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.022694685857930885</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.018504240555127227</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.044276632787057367</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>0.097526154321808542</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -3594,37 +3712,37 @@
         </x:is>
       </x:c>
       <x:c s="8">
-        <x:v>473.48346877892612</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0013787452979268089</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0028358918680937428</x:v>
-      </x:c>
-      <x:c s="9">
-        <x:v>0.0028278647901471832</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0031773359655216105</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.005403522443305997</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.022360639277337446</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.035670789011530868</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.015733010181553597</x:v>
-      </x:c>
-      <x:c s="10">
-        <x:v>0.0033725035660809519</x:v>
-      </x:c>
-      <x:c s="11">
-        <x:v>0.62039887096282165</x:v>
+        <x:v>475.75353229899025</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.00023792477534612111</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>-0.00025735836062978912</x:v>
+      </x:c>
+      <x:c s="9">
+        <x:v>0.0010289548833002371</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0033529251909278912</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0033448939744509243</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.02288773899798624</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.036204751062298035</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.028485222024466239</x:v>
+      </x:c>
+      <x:c s="10">
+        <x:v>0.0043333306494063471</x:v>
+      </x:c>
+      <x:c s="11">
+        <x:v>1.3050350750212265</x:v>
       </x:c>
     </x:row>
     <x:row/>
@@ -3634,7 +3752,7 @@
           <x:t>Filtros aplicados: 
 vcp_last no es 0
 Incluido (3) Renta Mixta (Clasifica_1), Renta Fija (Clasifica_1) + ARS (Clasifica_Moneda), Renta Fija (Clasifica_1) + USD (Clasifica_Moneda) + Corto Plazo (Clasifica_2)
-Soc. Gerente es 0
+Dedicado es 0
 Soc. Gerente es Delta, Galileo, Industria, Peers, Benchmark, Schroder o Investis
 Clase_Tipo_Delta es Clase Única o Mayorista
 Activo es 1
@@ -3651,14 +3769,14 @@
     <x:mergeCell ref="C35:C38"/>
     <x:mergeCell ref="C39:C47"/>
     <x:mergeCell ref="B2:B47"/>
-    <x:mergeCell ref="C48:C60"/>
-    <x:mergeCell ref="B48:B60"/>
-    <x:mergeCell ref="A2:A60"/>
-    <x:mergeCell ref="C61:C62"/>
-    <x:mergeCell ref="B61:B62"/>
-    <x:mergeCell ref="C63:C65"/>
-    <x:mergeCell ref="B63:B65"/>
-    <x:mergeCell ref="A61:A65"/>
+    <x:mergeCell ref="C48:C62"/>
+    <x:mergeCell ref="B48:B62"/>
+    <x:mergeCell ref="A2:A62"/>
+    <x:mergeCell ref="C63:C64"/>
+    <x:mergeCell ref="B63:B64"/>
+    <x:mergeCell ref="C65:C67"/>
+    <x:mergeCell ref="B65:B67"/>
+    <x:mergeCell ref="A63:A67"/>
   </x:mergeCells>
 </x:worksheet>
 </file>
@@ -3924,13 +4042,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02E3521B-B3E0-46B3-B555-DD093966BE84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B8613C6E-E4E3-442B-A0D4-6361178821F3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6679922B-37BB-45EE-8998-08FBFCBA37ED}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{892463D3-E652-44C0-AD25-C3B3DFC1E8C4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10FBF7C7-CF88-4DDA-A941-23BBE0FB286A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF56BB01-2E27-4283-9CEC-3BBA7FB34AC4}"/>
 </file>